--- a/final_correct_sections.xlsx
+++ b/final_correct_sections.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aliuz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aliuz\Desktop\VSCodes\Old version\giki_scheduler_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEEC99E-3886-4EF4-A556-904F71422DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0C3674-1F3D-4AE4-BEFD-B18682C4FBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="263">
   <si>
     <t>Sem.</t>
   </si>
@@ -1305,7 +1305,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="11.53125" customWidth="1"/>
@@ -1675,10 +1675,10 @@
         <v>34</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
@@ -1694,14 +1694,14 @@
       <c r="D17" s="3">
         <v>1</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>34</v>
+      <c r="E17" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>261</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
@@ -1717,14 +1717,14 @@
       <c r="D18" s="3">
         <v>1</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>35</v>
+      <c r="E18" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
@@ -1740,14 +1740,14 @@
       <c r="D19" s="3">
         <v>1</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>34</v>
+      <c r="E19" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
@@ -1763,14 +1763,14 @@
       <c r="D20" s="3">
         <v>1</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>23</v>
+      <c r="E20" s="8" t="s">
+        <v>36</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
@@ -1786,14 +1786,14 @@
       <c r="D21" s="3">
         <v>1</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>36</v>
+      <c r="E21" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
@@ -1810,16 +1810,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3">
         <v>2</v>
       </c>
@@ -1832,14 +1832,14 @@
       <c r="D23" s="3">
         <v>1</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>37</v>
+      <c r="E23" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G23" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
@@ -1847,45 +1847,45 @@
         <v>2</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>36</v>
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G24" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="121.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="3">
         <v>2</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>32</v>
+      <c r="B25" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>38</v>
+      <c r="E25" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
@@ -1893,45 +1893,45 @@
         <v>2</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D26" s="3">
         <v>1</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>39</v>
+      <c r="E26" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G26" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" s="3">
         <v>2</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D27" s="3">
         <v>1</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>40</v>
+      <c r="E27" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G27" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
@@ -1939,45 +1939,45 @@
         <v>2</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D28" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G28" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="121.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" s="3">
         <v>2</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>44</v>
+      <c r="B29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="D29" s="3">
         <v>1</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>45</v>
+      <c r="E29" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G29" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
@@ -1994,13 +1994,13 @@
         <v>1</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
@@ -2017,13 +2017,13 @@
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
@@ -2040,105 +2040,105 @@
         <v>1</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>27</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A33" s="3">
-        <v>2</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="3">
-        <v>1</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>48</v>
+      <c r="A33" s="12">
+        <v>4</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33" s="12">
+        <v>3</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>52</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A34" s="3">
-        <v>2</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>48</v>
+      <c r="A34" s="12">
+        <v>4</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="12">
+        <v>3</v>
+      </c>
+      <c r="E34" s="14" t="s">
+        <v>55</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A35" s="3">
-        <v>2</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="3">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>39</v>
+      <c r="A35" s="12">
+        <v>4</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="12">
+        <v>3</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>58</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A36" s="3">
-        <v>2</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="3">
-        <v>1</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>49</v>
+      <c r="A36" s="12">
+        <v>4</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D36" s="12">
+        <v>3</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>9</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
@@ -2146,22 +2146,22 @@
         <v>4</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D37" s="12">
-        <v>3</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>63</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G37" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
@@ -2169,22 +2169,22 @@
         <v>4</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D38" s="12">
-        <v>3</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>55</v>
+        <v>1</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
@@ -2192,22 +2192,22 @@
         <v>4</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D39" s="12">
-        <v>3</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G39" t="s">
-        <v>261</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
@@ -2215,22 +2215,22 @@
         <v>4</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D40" s="12">
         <v>3</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
@@ -2238,22 +2238,22 @@
         <v>4</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D41" s="12">
-        <v>1</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>63</v>
+        <v>3</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>73</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
@@ -2261,22 +2261,22 @@
         <v>4</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D42" s="12">
-        <v>1</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>66</v>
+        <v>3</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G42" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
@@ -2284,22 +2284,22 @@
         <v>4</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D43" s="12">
-        <v>1</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>69</v>
+        <v>3</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>77</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>27</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
@@ -2307,22 +2307,22 @@
         <v>4</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D44" s="12">
-        <v>3</v>
-      </c>
-      <c r="E44" s="14" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>78</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G44" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
@@ -2330,22 +2330,22 @@
         <v>4</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="D45" s="12">
-        <v>3</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>73</v>
+        <v>1</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G45" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
@@ -2353,137 +2353,137 @@
         <v>4</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D46" s="12">
-        <v>3</v>
-      </c>
-      <c r="E46" s="14" t="s">
-        <v>76</v>
+        <v>1</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>66</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A47" s="12">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="108" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="16">
         <v>4</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="3">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48" s="3">
+        <v>4</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G48" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="3">
+        <v>4</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C49" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D47" s="12">
-        <v>3</v>
-      </c>
-      <c r="E47" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G47" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A48" s="12">
+      <c r="D49" s="3">
+        <v>3</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="3">
         <v>4</v>
       </c>
-      <c r="B48" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="12">
-        <v>1</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A49" s="12">
+      <c r="B50" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="3">
+        <v>1</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="3">
         <v>4</v>
       </c>
-      <c r="B49" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49" s="12">
-        <v>1</v>
-      </c>
-      <c r="E49" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G49" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A50" s="12">
-        <v>4</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D50" s="12">
-        <v>1</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G50" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="108" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="16">
-        <v>4</v>
-      </c>
       <c r="B51" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>82</v>
+        <v>88</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="D51" s="3">
         <v>3</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>83</v>
+      <c r="E51" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G51" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
@@ -2491,45 +2491,45 @@
         <v>4</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>85</v>
+      <c r="E52" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A53" s="3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="108" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="16">
         <v>4</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>82</v>
       </c>
       <c r="D53" s="3">
         <v>3</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>86</v>
+      <c r="E53" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G53" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
@@ -2537,22 +2537,22 @@
         <v>4</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>87</v>
+      <c r="E54" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>27</v>
+        <v>254</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
@@ -2560,22 +2560,22 @@
         <v>4</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="D55" s="3">
         <v>3</v>
       </c>
-      <c r="E55" s="7" t="s">
-        <v>90</v>
+      <c r="E55" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G55" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
@@ -2583,45 +2583,45 @@
         <v>4</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
       </c>
-      <c r="E56" s="9" t="s">
-        <v>93</v>
+      <c r="E56" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="108" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="16">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" s="3">
         <v>4</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>82</v>
+        <v>95</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="D57" s="3">
         <v>3</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
@@ -2629,22 +2629,22 @@
         <v>4</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D58" s="3">
-        <v>1</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>94</v>
+        <v>3</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G58" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
@@ -2652,22 +2652,20 @@
         <v>4</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="D59" s="3">
-        <v>3</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>86</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E59" s="5"/>
       <c r="F59" s="6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G59" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
@@ -2675,45 +2673,45 @@
         <v>4</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D60" s="3">
         <v>1</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>87</v>
+      <c r="E60" s="3" t="s">
+        <v>104</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A61" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="108" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="16">
         <v>4</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>96</v>
+        <v>50</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>82</v>
       </c>
       <c r="D61" s="3">
         <v>3</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>97</v>
+      <c r="E61" s="3" t="s">
+        <v>105</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G61" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
@@ -2721,22 +2719,22 @@
         <v>4</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>98</v>
+        <v>61</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D62" s="3">
-        <v>3</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G62" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
@@ -2744,20 +2742,22 @@
         <v>4</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="D63" s="3">
-        <v>2</v>
-      </c>
-      <c r="E63" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>107</v>
+      </c>
       <c r="F63" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
@@ -2765,39 +2765,39 @@
         <v>4</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G64" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="108" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="16">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A65" s="3">
         <v>4</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>82</v>
+        <v>108</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="D65" s="3">
         <v>3</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>105</v>
+      <c r="E65" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>30</v>
@@ -2811,22 +2811,22 @@
         <v>4</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D66" s="3">
-        <v>1</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>106</v>
+        <v>3</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
@@ -2834,22 +2834,22 @@
         <v>4</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D67" s="3">
         <v>3</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>107</v>
+      <c r="E67" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G67" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
@@ -2857,22 +2857,22 @@
         <v>4</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
@@ -2880,22 +2880,22 @@
         <v>4</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D69" s="3">
-        <v>3</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>110</v>
+        <v>2</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G69" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
@@ -2903,22 +2903,22 @@
         <v>4</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D70" s="3">
         <v>3</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G70" t="s">
-        <v>254</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
@@ -2926,22 +2926,22 @@
         <v>4</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D71" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G71" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
@@ -2949,22 +2949,22 @@
         <v>4</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="D72" s="3">
-        <v>1</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>115</v>
+        <v>3</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G72" t="s">
-        <v>261</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
@@ -2972,114 +2972,114 @@
         <v>4</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="D73" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>118</v>
+        <v>40</v>
       </c>
       <c r="F73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G73" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A74" s="12">
+        <v>6</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" s="12">
+        <v>3</v>
+      </c>
+      <c r="E74" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A75" s="12">
+        <v>6</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D75" s="12">
+        <v>3</v>
+      </c>
+      <c r="E75" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G75" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A76" s="12">
+        <v>6</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D76" s="12">
+        <v>3</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A77" s="12">
+        <v>6</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D77" s="12">
+        <v>3</v>
+      </c>
+      <c r="E77" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="F77" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G73" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A74" s="3">
-        <v>4</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D74" s="3">
-        <v>3</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G74" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A75" s="3">
-        <v>4</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D75" s="3">
-        <v>1</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A76" s="3">
-        <v>4</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D76" s="3">
-        <v>3</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G76" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A77" s="3">
-        <v>4</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D77" s="3">
-        <v>1</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="G77" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
@@ -3087,22 +3087,22 @@
         <v>6</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D78" s="12">
         <v>3</v>
       </c>
-      <c r="E78" s="14" t="s">
-        <v>58</v>
+      <c r="E78" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G78" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
@@ -3110,22 +3110,22 @@
         <v>6</v>
       </c>
       <c r="B79" s="13" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="D79" s="12">
         <v>3</v>
       </c>
-      <c r="E79" s="18" t="s">
-        <v>127</v>
+      <c r="E79" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
@@ -3133,22 +3133,22 @@
         <v>6</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="D80" s="12">
         <v>3</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G80" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
@@ -3156,45 +3156,45 @@
         <v>6</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>131</v>
+        <v>140</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>141</v>
       </c>
       <c r="D81" s="12">
-        <v>3</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>132</v>
+        <v>1</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>142</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G81" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A82" s="12">
-        <v>6</v>
-      </c>
-      <c r="B82" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D82" s="12">
-        <v>3</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>127</v>
+      <c r="A82" s="14">
+        <v>6</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D82" s="14">
+        <v>1</v>
+      </c>
+      <c r="E82" s="15" t="s">
+        <v>262</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G82" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
@@ -3202,22 +3202,22 @@
         <v>6</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D83" s="12">
         <v>3</v>
       </c>
-      <c r="E83" s="12" t="s">
-        <v>25</v>
+      <c r="E83" s="18" t="s">
+        <v>145</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G83" t="s">
-        <v>261</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
@@ -3225,22 +3225,22 @@
         <v>6</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D84" s="12">
         <v>3</v>
       </c>
       <c r="E84" s="14" t="s">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G84" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
@@ -3248,45 +3248,45 @@
         <v>6</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C85" s="19" t="s">
-        <v>141</v>
+        <v>146</v>
+      </c>
+      <c r="C85" s="13" t="s">
+        <v>147</v>
       </c>
       <c r="D85" s="12">
-        <v>1</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>142</v>
+        <v>3</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G85" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A86" s="14">
-        <v>6</v>
-      </c>
-      <c r="B86" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="C86" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D86" s="14">
-        <v>1</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>262</v>
+      <c r="A86" s="12">
+        <v>6</v>
+      </c>
+      <c r="B86" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D86" s="12">
+        <v>3</v>
+      </c>
+      <c r="E86" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G86" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
@@ -3294,22 +3294,22 @@
         <v>6</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="D87" s="12">
         <v>3</v>
       </c>
-      <c r="E87" s="18" t="s">
-        <v>145</v>
+      <c r="E87" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>27</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.45">
@@ -3317,22 +3317,22 @@
         <v>6</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="D88" s="12">
         <v>3</v>
       </c>
-      <c r="E88" s="14" t="s">
-        <v>77</v>
+      <c r="E88" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
@@ -3340,22 +3340,22 @@
         <v>6</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D89" s="12">
         <v>3</v>
       </c>
-      <c r="E89" s="14" t="s">
-        <v>76</v>
+      <c r="E89" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G89" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
@@ -3363,114 +3363,114 @@
         <v>6</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="D90" s="12">
         <v>3</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>132</v>
+        <v>70</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A91" s="12">
-        <v>6</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D91" s="12">
-        <v>3</v>
-      </c>
-      <c r="E91" s="12" t="s">
-        <v>149</v>
+      <c r="A91" s="3">
+        <v>6</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D91" s="3">
+        <v>3</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G91" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A92" s="12">
-        <v>6</v>
-      </c>
-      <c r="B92" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D92" s="12">
-        <v>3</v>
-      </c>
-      <c r="E92" s="12" t="s">
-        <v>152</v>
+      <c r="A92" s="3">
+        <v>6</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D92" s="3">
+        <v>3</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G92" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A93" s="12">
-        <v>6</v>
-      </c>
-      <c r="B93" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D93" s="12">
-        <v>3</v>
-      </c>
-      <c r="E93" s="12" t="s">
-        <v>25</v>
+      <c r="A93" s="3">
+        <v>6</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D93" s="3">
+        <v>1</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>163</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G93" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A94" s="12">
-        <v>6</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D94" s="12">
-        <v>3</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>70</v>
+      <c r="A94" s="3">
+        <v>6</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D94" s="3">
+        <v>3</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G94" t="s">
-        <v>261</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
@@ -3478,22 +3478,22 @@
         <v>6</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D95" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G95" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
@@ -3501,22 +3501,22 @@
         <v>6</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D96" s="3">
-        <v>3</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>160</v>
+        <v>1</v>
+      </c>
+      <c r="E96" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G96" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
@@ -3524,22 +3524,22 @@
         <v>6</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="D97" s="3">
-        <v>1</v>
-      </c>
-      <c r="E97" s="9" t="s">
-        <v>163</v>
+        <v>3</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G97" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
@@ -3547,45 +3547,45 @@
         <v>6</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="D98" s="3">
         <v>3</v>
       </c>
-      <c r="E98" s="7" t="s">
-        <v>157</v>
+      <c r="E98" s="5" t="s">
+        <v>172</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="94.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="3">
         <v>6</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D99" s="3">
-        <v>2</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>168</v>
+        <v>3</v>
+      </c>
+      <c r="E99" s="20" t="s">
+        <v>175</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G99" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
@@ -3593,22 +3593,22 @@
         <v>6</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="D100" s="3">
-        <v>1</v>
-      </c>
-      <c r="E100" s="9" t="s">
-        <v>93</v>
+        <v>3</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
@@ -3616,22 +3616,22 @@
         <v>6</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="D101" s="3">
-        <v>3</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>171</v>
+        <v>2</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G101" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
@@ -3639,45 +3639,45 @@
         <v>6</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="D102" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G102" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="94.5" customHeight="1" x14ac:dyDescent="0.45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" s="3">
         <v>6</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D103" s="3">
         <v>3</v>
       </c>
-      <c r="E103" s="20" t="s">
-        <v>175</v>
+      <c r="E103" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G103" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
@@ -3685,22 +3685,22 @@
         <v>6</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>130</v>
+        <v>185</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D104" s="3">
+        <v>186</v>
+      </c>
+      <c r="D104" s="5">
         <v>3</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G104" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
@@ -3708,22 +3708,22 @@
         <v>6</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>176</v>
+        <v>125</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="D105" s="3">
-        <v>2</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>178</v>
+        <v>3</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G105" t="s">
-        <v>261</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
@@ -3731,22 +3731,22 @@
         <v>6</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="D106" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G106" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
@@ -3754,22 +3754,22 @@
         <v>6</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>182</v>
+        <v>130</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="D107" s="3">
         <v>3</v>
       </c>
-      <c r="E107" s="7" t="s">
-        <v>184</v>
+      <c r="E107" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G107" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
@@ -3777,22 +3777,22 @@
         <v>6</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="D108" s="5">
+        <v>189</v>
+      </c>
+      <c r="D108" s="3">
         <v>3</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>104</v>
+        <v>255</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G108" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
@@ -3800,22 +3800,22 @@
         <v>6</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="D109" s="3">
-        <v>3</v>
-      </c>
-      <c r="E109" s="5" t="s">
-        <v>110</v>
+        <v>1</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>192</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G109" t="s">
-        <v>27</v>
+        <v>254</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
@@ -3823,22 +3823,22 @@
         <v>6</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>128</v>
+        <v>193</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="D110" s="3">
         <v>3</v>
       </c>
-      <c r="E110" s="5" t="s">
-        <v>187</v>
+      <c r="E110" s="9" t="s">
+        <v>113</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G110" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
@@ -3846,22 +3846,22 @@
         <v>6</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="D111" s="3">
         <v>3</v>
       </c>
-      <c r="E111" s="5" t="s">
-        <v>118</v>
+      <c r="E111" s="9" t="s">
+        <v>197</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G111" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
@@ -3869,22 +3869,22 @@
         <v>6</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>188</v>
+        <v>125</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="D112" s="3">
         <v>3</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>255</v>
+        <v>110</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G112" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
@@ -3892,22 +3892,22 @@
         <v>6</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>190</v>
+        <v>128</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>191</v>
+        <v>129</v>
       </c>
       <c r="D113" s="3">
-        <v>1</v>
-      </c>
-      <c r="E113" s="3" t="s">
-        <v>192</v>
+        <v>3</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G113" t="s">
-        <v>254</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.45">
@@ -3915,252 +3915,252 @@
         <v>6</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="D114" s="3">
         <v>3</v>
       </c>
-      <c r="E114" s="9" t="s">
-        <v>113</v>
+      <c r="E114" s="3" t="s">
+        <v>198</v>
       </c>
       <c r="F114" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G114" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A115" s="21">
+        <v>6</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D115" s="3">
+        <v>3</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A116" s="21">
+        <v>6</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D116" s="3">
+        <v>1</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A117" s="21">
+        <v>6</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D117" s="3">
+        <v>3</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G117" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A118" s="21">
+        <v>6</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D118" s="3">
+        <v>3</v>
+      </c>
+      <c r="E118" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G118" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A119" s="3">
+        <v>6</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D119" s="3">
+        <v>2</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G119" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A120" s="3">
+        <v>6</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D120" s="3">
+        <v>2</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A121" s="12">
+        <v>8</v>
+      </c>
+      <c r="B121" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C121" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="D121" s="12">
+        <v>3</v>
+      </c>
+      <c r="E121" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G121" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A122" s="12">
+        <v>8</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C122" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="D122" s="12">
+        <v>3</v>
+      </c>
+      <c r="E122" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A123" s="12">
+        <v>8</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D123" s="12">
+        <v>3</v>
+      </c>
+      <c r="E123" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G123" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A124" s="12">
+        <v>8</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="C124" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D124" s="12">
+        <v>3</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F124" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G114" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A115" s="3">
-        <v>6</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D115" s="3">
-        <v>3</v>
-      </c>
-      <c r="E115" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G115" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A116" s="3">
-        <v>6</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D116" s="3">
-        <v>3</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G116" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A117" s="3">
-        <v>6</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D117" s="3">
-        <v>3</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G117" t="s">
+      <c r="G124" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A118" s="3">
-        <v>6</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D118" s="3">
-        <v>3</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G118" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A119" s="21">
-        <v>6</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D119" s="3">
-        <v>3</v>
-      </c>
-      <c r="E119" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A120" s="21">
-        <v>6</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D120" s="3">
-        <v>1</v>
-      </c>
-      <c r="E120" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G120" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A121" s="21">
-        <v>6</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="D121" s="3">
-        <v>3</v>
-      </c>
-      <c r="E121" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G121" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A122" s="21">
-        <v>6</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D122" s="3">
-        <v>3</v>
-      </c>
-      <c r="E122" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G122" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A123" s="3">
-        <v>6</v>
-      </c>
-      <c r="B123" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="C123" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="D123" s="3">
-        <v>2</v>
-      </c>
-      <c r="E123" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A124" s="3">
-        <v>6</v>
-      </c>
-      <c r="B124" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="C124" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="D124" s="3">
-        <v>2</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G124" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
@@ -4168,22 +4168,22 @@
         <v>8</v>
       </c>
       <c r="B125" s="13" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C125" s="13" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D125" s="12">
         <v>3</v>
       </c>
-      <c r="E125" s="18" t="s">
-        <v>18</v>
+      <c r="E125" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G125" t="s">
-        <v>257</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
@@ -4191,22 +4191,22 @@
         <v>8</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="C126" s="13" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="D126" s="12">
-        <v>3</v>
-      </c>
-      <c r="E126" s="14" t="s">
-        <v>214</v>
+        <v>1</v>
+      </c>
+      <c r="E126" s="22" t="s">
+        <v>262</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G126" t="s">
-        <v>259</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.45">
@@ -4214,22 +4214,22 @@
         <v>8</v>
       </c>
       <c r="B127" s="13" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C127" s="13" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D127" s="12">
         <v>3</v>
       </c>
       <c r="E127" s="18" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G127" t="s">
-        <v>261</v>
+        <v>27</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.45">
@@ -4237,22 +4237,22 @@
         <v>8</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C128" s="13" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D128" s="12">
         <v>3</v>
       </c>
-      <c r="E128" s="14" t="s">
-        <v>197</v>
+      <c r="E128" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G128" t="s">
-        <v>11</v>
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.45">
@@ -4260,22 +4260,22 @@
         <v>8</v>
       </c>
       <c r="B129" s="13" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C129" s="13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D129" s="12">
         <v>3</v>
       </c>
       <c r="E129" s="14" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G129" t="s">
-        <v>16</v>
+        <v>256</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
@@ -4283,22 +4283,22 @@
         <v>8</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C130" s="13" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D130" s="12">
-        <v>1</v>
-      </c>
-      <c r="E130" s="22" t="s">
-        <v>262</v>
+        <v>3</v>
+      </c>
+      <c r="E130" s="18" t="s">
+        <v>73</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G130" t="s">
-        <v>14</v>
+        <v>253</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.45">
@@ -4306,22 +4306,22 @@
         <v>8</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="C131" s="13" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="D131" s="12">
         <v>3</v>
       </c>
       <c r="E131" s="18" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G131" t="s">
-        <v>27</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.45">
@@ -4329,22 +4329,22 @@
         <v>8</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C132" s="13" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D132" s="12">
         <v>3</v>
       </c>
-      <c r="E132" s="18" t="s">
-        <v>132</v>
+      <c r="E132" s="14" t="s">
+        <v>76</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="G132" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.45">
@@ -4352,114 +4352,114 @@
         <v>8</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D133" s="12">
-        <v>3</v>
-      </c>
-      <c r="E133" s="14" t="s">
-        <v>214</v>
+        <v>1</v>
+      </c>
+      <c r="E133" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="F133" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A134" s="3">
+        <v>8</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="D134" s="3">
+        <v>3</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G134" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A135" s="3">
+        <v>8</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D135" s="3">
+        <v>1</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G135" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A136" s="3">
+        <v>8</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D136" s="3">
+        <v>3</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G133" t="s">
+      <c r="G136" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A134" s="12">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A137" s="3">
         <v>8</v>
       </c>
-      <c r="B134" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C134" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D134" s="12">
-        <v>3</v>
-      </c>
-      <c r="E134" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G134" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A135" s="12">
-        <v>8</v>
-      </c>
-      <c r="B135" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="C135" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="D135" s="12">
-        <v>3</v>
-      </c>
-      <c r="E135" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G135" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A136" s="12">
-        <v>8</v>
-      </c>
-      <c r="B136" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="C136" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="D136" s="12">
-        <v>3</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G136" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A137" s="12">
-        <v>8</v>
-      </c>
-      <c r="B137" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="C137" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="D137" s="12">
-        <v>1</v>
-      </c>
-      <c r="E137" s="12" t="s">
-        <v>69</v>
+      <c r="B137" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D137" s="3">
+        <v>3</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G137" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.45">
@@ -4467,22 +4467,22 @@
         <v>8</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="D138" s="3">
         <v>3</v>
       </c>
-      <c r="E138" s="5" t="s">
-        <v>104</v>
+      <c r="E138" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G138" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.45">
@@ -4490,16 +4490,16 @@
         <v>8</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="D139" s="3">
-        <v>1</v>
-      </c>
-      <c r="E139" s="3" t="s">
-        <v>104</v>
+        <v>3</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>10</v>
@@ -4513,22 +4513,22 @@
         <v>8</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="D140" s="3">
         <v>3</v>
       </c>
-      <c r="E140" s="5" t="s">
-        <v>234</v>
+      <c r="E140" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="G140" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.45">
@@ -4536,22 +4536,22 @@
         <v>8</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D141" s="3">
         <v>3</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G141" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.45">
@@ -4559,16 +4559,16 @@
         <v>8</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>211</v>
+        <v>129</v>
       </c>
       <c r="D142" s="3">
         <v>3</v>
       </c>
-      <c r="E142" s="7" t="s">
-        <v>184</v>
+      <c r="E142" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>24</v>
@@ -4582,22 +4582,22 @@
         <v>8</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D143" s="3">
         <v>3</v>
       </c>
-      <c r="E143" s="7" t="s">
-        <v>178</v>
+      <c r="E143" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G143" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.45">
@@ -4605,22 +4605,22 @@
         <v>8</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D144" s="3">
         <v>3</v>
       </c>
-      <c r="E144" s="7" t="s">
-        <v>160</v>
+      <c r="E144" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G144" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.45">
@@ -4628,16 +4628,16 @@
         <v>8</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D145" s="3">
         <v>3</v>
       </c>
-      <c r="E145" s="7" t="s">
-        <v>97</v>
+      <c r="E145" s="5" t="s">
+        <v>255</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>28</v>
@@ -4651,113 +4651,21 @@
         <v>8</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>129</v>
+        <v>248</v>
+      </c>
+      <c r="C146" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="D146" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G146" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A147" s="3">
-        <v>8</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D147" s="3">
-        <v>3</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G147" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A148" s="3">
-        <v>8</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="D148" s="3">
-        <v>3</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G148" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A149" s="3">
-        <v>8</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D149" s="3">
-        <v>3</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G149" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A150" s="3">
-        <v>8</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D150" s="3">
-        <v>1</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G150" t="s">
         <v>254</v>
       </c>
     </row>
